--- a/data/trans_dic/IP11D_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún tipo de agresión</t>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,73</t>
+          <t>0,8; 6,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,33</t>
+          <t>0,63; 4,08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,82</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,43</t>
+          <t>1,07; 9,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,5</t>
+          <t>0,62; 5,58</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,93</t>
+          <t>0,0; 8,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 18,56</t>
+          <t>0,69; 18,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,86</t>
+          <t>1,31; 11,66</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,6</t>
+          <t>0,44; 4,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,59</t>
+          <t>0,27; 2,56</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,63</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,35</t>
+          <t>0,64; 2,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,76</t>
+          <t>0,64; 1,72</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5389</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1021; 8451</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1611; 10385</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4052</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>716; 6690</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>779; 7005</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3986</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>388; 10622</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1340; 11933</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>550; 5781</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4298</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>750; 7144</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9687</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2137; 10110</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4904; 18281</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>9056; 24495</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11D_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Provincia-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,62</t>
+          <t>0,72; 6,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,08</t>
+          <t>0,66; 4,05</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,96</t>
+          <t>1,04; 9,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,58</t>
+          <t>0,67; 6,08</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,63</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 18,91</t>
+          <t>0,67; 17,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,66</t>
+          <t>1,36; 11,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,64</t>
+          <t>0,47; 4,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,56</t>
+          <t>0,28; 2,44</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,52</t>
+          <t>0,37; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,63; 2,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,72</t>
+          <t>0,64; 1,71</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5389</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1021; 8451</t>
+          <t>923; 8381</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1611; 10385</t>
+          <t>1674; 10298</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4052</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>716; 6690</t>
+          <t>697; 6341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>779; 7005</t>
+          <t>845; 7622</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3986</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>388; 10622</t>
+          <t>378; 9698</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1340; 11933</t>
+          <t>1394; 11610</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>550; 5781</t>
+          <t>581; 5765</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>0; 4420</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>750; 7144</t>
+          <t>773; 6824</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2137; 10110</t>
+          <t>2489; 10120</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4904; 18281</t>
+          <t>4791; 17811</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9056; 24495</t>
+          <t>9123; 24445</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11D_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,78; 6,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,57</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,05</t>
+          <t>0,81; 4,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>1,07; 9,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,44</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,08</t>
+          <t>0,56; 5,23</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>1,06; 18,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 17,26</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,34</t>
+          <t>1,2; 11,67</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,63</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,5; 4,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,44</t>
+          <t>0,3; 2,78</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,52</t>
+          <t>0,63; 2,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,34</t>
+          <t>0,38; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,71</t>
+          <t>0,68; 1,75</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4542</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>899; 7963</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>923; 8381</t>
+          <t>0; 4529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1674; 10298</t>
+          <t>1755; 10377</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2664</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3015</t>
+          <t>636; 5417</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>697; 6341</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>845; 7622</t>
+          <t>649; 6060</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3781</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4414</t>
+          <t>517; 9034</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>378; 9698</t>
+          <t>0; 3850</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1394; 11610</t>
+          <t>1137; 11057</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>863</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3102</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>581; 5765</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4420</t>
+          <t>611; 6066</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>773; 6824</t>
+          <t>795; 7297</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2489; 10120</t>
+          <t>4394; 16081</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4791; 17811</t>
+          <t>2419; 10719</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9123; 24445</t>
+          <t>9040; 23271</t>
         </is>
       </c>
     </row>
